--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -433,10 +433,10 @@
         <v>Espacio Oliva</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="str">
         <v>https://i.postimg.cc/wTK4jZmv/Whats-App-Image-2026-07-08-at-9-22-00-PM.jpg</v>
@@ -453,10 +453,10 @@
         <v>Espacio Oliva</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
         <v>https://i.postimg.cc/pdxpVWWt/Whats-App-Image-2026-07-08-at-9-22-00-PM-(1).jpg</v>
@@ -473,10 +473,10 @@
         <v>Espacio Oliva</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="str">
         <v>https://i.postimg.cc/tT4JPBnS/Whats-App-Image-2026-07-08-at-9-22-00-PM-(2).jpg</v>
@@ -493,10 +493,10 @@
         <v>Espacio Oliva</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="str">
         <v>https://i.postimg.cc/8cFCXsHr/Whats-App-Image-2026-07-08-at-9-22-01-PM.jpg</v>
@@ -513,10 +513,10 @@
         <v>Espacio Oliva</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="str">
         <v>https://i.postimg.cc/x8W1wYx5/Whats-App-Image-2026-07-08-at-9-22-02-PM.jpg</v>
@@ -533,10 +533,10 @@
         <v>Espacio Oliva</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
         <v>https://i.postimg.cc/VsTvrBfS/Whats-App-Image-2026-07-08-at-9-22-02-PM-(1).jpg</v>
@@ -553,10 +553,10 @@
         <v>Espacio Oliva</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="str">
         <v>https://i.postimg.cc/MGWp29DN/Whats-App-Image-2026-07-08-at-9-22-02-PM-(2).jpg</v>
@@ -573,10 +573,10 @@
         <v>Espacio Oliva</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="str">
         <v>https://i.postimg.cc/3Rq8GYTy/Whats-App-Image-2026-07-08-at-9-22-03-PM.jpg</v>
@@ -593,10 +593,10 @@
         <v>Espacio Oliva</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
         <v>https://i.postimg.cc/MpYjQMrf/Whats-App-Image-2026-07-08-at-9-22-04-PM-(1).jpg</v>
@@ -613,10 +613,10 @@
         <v>Espacio Oliva</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="str">
         <v>https://i.postimg.cc/MGKfb6hd/Whats-App-Image-2026-07-08-at-9-22-05-PM.jpg</v>
@@ -633,10 +633,10 @@
         <v>Espacio Oliva</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" t="str">
         <v>https://i.postimg.cc/rpn0h6TX/Whats-App-Image-2026-07-08-at-9-22-05-PM-(1).jpg</v>

--- a/data/catalogo.xlsx
+++ b/data/catalogo.xlsx
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Croquetas de arroz con puré mixto cremoso</v>
+        <v>holaholas</v>
       </c>
       <c r="B2" t="str">
         <v>Viandas empresariales</v>
@@ -640,6 +640,14 @@
       </c>
       <c r="F12" t="str">
         <v>https://i.postimg.cc/rpn0h6TX/Whats-App-Image-2026-07-08-at-9-22-05-PM-(1).jpg</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="str">
+        <v>Viandas empresariales</v>
+      </c>
+      <c r="F13" t="str">
+        <v>https://i.postimg.cc/Bn9zFk64/Chat-GPT-Image-25-jul-2026-09-15-27-p-m.png</v>
       </c>
     </row>
   </sheetData>
@@ -655,6 +663,7 @@
     <hyperlink ref="F10" r:id="rId9"/>
     <hyperlink ref="F11" r:id="rId10"/>
     <hyperlink ref="F12" r:id="rId11"/>
+    <hyperlink ref="F13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <ignoredErrors>
